--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>4.09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>3.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O6" t="n">
-        <v>4.09</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>3.57</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4.09</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>3.57</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>4.09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>3.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>1.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1847,34 +1847,34 @@
         <v>4.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA9" t="n">
         <v>2.45</v>
@@ -1883,19 +1883,19 @@
         <v>1.49</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,34 +2006,34 @@
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.77</v>
@@ -2042,19 +2042,19 @@
         <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.9</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>3.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O6" t="n">
-        <v>4.09</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>3.57</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.13</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.93</v>
+        <v>1.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>6.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>3.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.13</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.9</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>3.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.52</v>
+        <v>6.99</v>
       </c>
       <c r="O7" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>5.66</v>
       </c>
       <c r="R7" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1838,34 +1838,34 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
         <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T9" t="n">
         <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1.1</v>
@@ -1874,28 +1874,28 @@
         <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
         <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.9</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>3.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>6.9</v>
       </c>
       <c r="O6" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>3.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.13</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
         <v>1.36</v>
@@ -1373,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
         <v>1.23</v>
@@ -1388,7 +1388,7 @@
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1418,7 +1418,7 @@
         <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.66</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="S7" t="n">
         <v>1.12</v>
@@ -1544,7 +1544,7 @@
         <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="W7" t="n">
         <v>1.36</v>
@@ -1562,10 +1562,10 @@
         <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
         <v>2.56</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O8" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
         <v>2.45</v>
@@ -1868,31 +1868,31 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
         <v>2.46</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
         <v>1.62</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
         <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>3.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
         <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.23</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU11"/>
+  <dimension ref="A1:AU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1632,27 +1632,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46205.67708333334</v>
+        <v>46205.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46205.83333333334</v>
+        <v>46205.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1950,27 +1950,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46205.875</v>
+        <v>46205.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2109,156 +2109,1428 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46205.58333333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RSB Berkane</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46205.58333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Olympique Dcheïra</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46205.58333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kawkab Marrakech</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Maghreb Fès</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>46205.58333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CR Khemis Zemamra</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46205.58333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>46205.67708333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>46205.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>46205.875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="3" t="n">
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="3" t="n">
         <v>46205.875</v>
       </c>
     </row>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="O4" t="n">
-        <v>4.71</v>
+        <v>4.37</v>
       </c>
       <c r="P4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>3.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
         <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.23</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>3.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>2.45</v>
@@ -1382,43 +1382,43 @@
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.88</v>
+        <v>4.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2960,25 +2960,25 @@
         <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
         <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>2.07</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF16" t="n">
         <v>1.71</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
         <v>5.2</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.77</v>
+        <v>3.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
         <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1235,31 +1235,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.88</v>
+        <v>5.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="R17" t="n">
         <v>2</v>
@@ -3128,37 +3128,37 @@
         <v>1.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
         <v>1.01</v>
@@ -3167,7 +3167,7 @@
         <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.63</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.27</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
         <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>3.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.27</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.15</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>6.15</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
         <v>2.6</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>3.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="U16" t="n">
         <v>1.75</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,25 +3110,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="Q17" t="n">
         <v>2.51</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S17" t="n">
         <v>1.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
         <v>3.6</v>
@@ -3137,16 +3137,16 @@
         <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AA17" t="n">
         <v>2.5</v>
@@ -3158,16 +3158,16 @@
         <v>4.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE17" t="n">
         <v>1.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
         <v>2.6</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3110,25 +3110,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="U17" t="n">
         <v>3.6</v>
@@ -3137,37 +3137,37 @@
         <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
         <v>1.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
         <v>1.9</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>6.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.13</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>6.3</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>4.37</v>
+        <v>4.14</v>
       </c>
       <c r="P4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
         <v>1.36</v>
@@ -1214,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
         <v>1.22</v>
@@ -1253,7 +1253,7 @@
         <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF5" t="n">
         <v>1.66</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
         <v>1.04</v>
@@ -1370,10 +1370,10 @@
         <v>3.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
@@ -1385,25 +1385,25 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC6" t="n">
         <v>2.25</v>
@@ -1418,7 +1418,7 @@
         <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>7.18</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2963,52 +2963,52 @@
         <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V16" t="n">
         <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
         <v>1.71</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P17" t="n">
-        <v>4.1</v>
+        <v>4.69</v>
       </c>
       <c r="Q17" t="n">
         <v>2.5</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU19"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46205.41666666666</v>
+        <v>46205.375</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46205.45833333334</v>
+        <v>46205.375</v>
       </c>
     </row>
     <row r="5">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>4.14</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>9.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46205.54166666666</v>
+        <v>46205.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>4.55</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46205.58333333334</v>
+        <v>46205.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.18</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>6.3</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.18</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.12</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46205.67708333334</v>
+        <v>46205.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="O17" t="n">
-        <v>3.18</v>
+        <v>8.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4.69</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V17" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.45</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>3.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.9</v>
+        <v>1.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.18</v>
+        <v>1.71</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.82</v>
+        <v>5.3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46205.83333333334</v>
+        <v>46205.67708333334</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>4.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46205.875</v>
+        <v>46205.83333333334</v>
       </c>
     </row>
     <row r="19">
@@ -3531,6 +3531,165 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
+        <v>46205.875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
         <v>46205.875</v>
       </c>
     </row>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>3.63</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>3.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
         <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.95</v>
+        <v>5.06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.18</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>7.18</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.18</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>7.18</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O5" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>9.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,22 +1361,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
         <v>3.75</v>
@@ -1406,10 +1406,10 @@
         <v>2.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
         <v>1.23</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>2.72</v>
       </c>
       <c r="AK6" t="n">
         <v>1.04</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2642,28 +2642,28 @@
         <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="U14" t="n">
         <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="W14" t="n">
         <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.04</v>
@@ -2672,19 +2672,19 @@
         <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB14" t="n">
         <v>5.21</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
         <v>2.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
         <v>1.3</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3113,34 +3113,34 @@
         <v>1.12</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>14.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
         <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.03</v>
@@ -3149,25 +3149,25 @@
         <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.3</v>
+        <v>4.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3272,13 +3272,13 @@
         <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>4.69</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
         <v>2</v>
@@ -3287,7 +3287,7 @@
         <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
         <v>3.6</v>
@@ -3296,10 +3296,10 @@
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.48</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
         <v>6.1</v>
@@ -1379,62 +1379,62 @@
         <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
         <v>1.12</v>
       </c>
       <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,34 +1520,34 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
@@ -1556,28 +1556,28 @@
         <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.06</v>
+        <v>5.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>1.39</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>5.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,25 +2633,25 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.18</v>
+        <v>7.37</v>
       </c>
       <c r="O14" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="R14" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="U14" t="n">
         <v>1.57</v>
@@ -2675,16 +2675,16 @@
         <v>1.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.21</v>
+        <v>5.26</v>
       </c>
       <c r="AC14" t="n">
         <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
         <v>1.3</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="P17" t="n">
-        <v>14.7</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.43</v>
+        <v>5.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O18" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
         <v>3.75</v>
@@ -3281,19 +3281,19 @@
         <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S18" t="n">
         <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
         <v>1.05</v>
@@ -3302,10 +3302,10 @@
         <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AA18" t="n">
         <v>2.45</v>
@@ -3314,19 +3314,19 @@
         <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
         <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -3440,52 +3440,52 @@
         <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
         <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
         <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
         <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="U9" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>3.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
         <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.44</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
         <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.75</v>
+        <v>1.39</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.08</v>
+        <v>2.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
         <v>1.44</v>
@@ -2510,13 +2510,13 @@
         <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>4.5</v>
@@ -2528,10 +2528,10 @@
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.37</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>6.4</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.3</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.57</v>
       </c>
-      <c r="V14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>5.26</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.62</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>3.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.39</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7.37</v>
+        <v>1.39</v>
       </c>
       <c r="O8" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="S8" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>6.5</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>3.12</v>
       </c>
       <c r="V8" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.11</v>
+        <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.26</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.38</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.62</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
         <v>2</v>
@@ -1856,46 +1856,46 @@
         <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="R12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.75</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AA13" t="n">
         <v>2.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD13" t="n">
         <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.08</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>7.37</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>6.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>5.26</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.95</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>5.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.48</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA16" t="n">
         <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P5" t="n">
-        <v>8.199999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>8.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3.39</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>5.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
         <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,37 +2315,37 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
@@ -2354,25 +2354,25 @@
         <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.37</v>
+        <v>5.75</v>
       </c>
       <c r="O14" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U14" t="n">
         <v>3.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.08</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.83</v>
       </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>1.14</v>
       </c>
       <c r="O17" t="n">
-        <v>8.35</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
         <v>1.41</v>
@@ -3125,19 +3125,19 @@
         <v>3.61</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -3146,16 +3146,16 @@
         <v>1.01</v>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AA17" t="n">
         <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
         <v>2.25</v>
@@ -3164,10 +3164,10 @@
         <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
         <v>3.75</v>
@@ -3290,10 +3290,10 @@
         <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
         <v>1.05</v>
@@ -3302,31 +3302,31 @@
         <v>1.1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC18" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE18" t="n">
         <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.4</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>3.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>8.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG8" t="n">
         <v>3.1</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.29</v>
@@ -1868,34 +1868,34 @@
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
         <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>5.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.29</v>
+        <v>7.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.04</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="AD13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.03</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>3.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>2.65</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>5.45</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="S15" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="T15" t="n">
-        <v>6.1</v>
+        <v>2.13</v>
       </c>
       <c r="U15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.57</v>
       </c>
-      <c r="V15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.17</v>
+        <v>2.32</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.37</v>
+        <v>4.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>8.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3.9</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>5.45</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>5.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>6.1</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.57</v>
       </c>
-      <c r="V8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.17</v>
       </c>
-      <c r="AB8" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>5.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="R10" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>6.1</v>
       </c>
       <c r="U10" t="n">
-        <v>3.02</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>2.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.09</v>
+        <v>1.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>5.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.58</v>
+        <v>1.37</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>2.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,37 +2315,37 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>3.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="R12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U12" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
         <v>1.37</v>
@@ -2354,25 +2354,25 @@
         <v>2.66</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,37 +2633,37 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.48</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="V14" t="n">
         <v>1.28</v>
       </c>
       <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.37</v>
@@ -2672,25 +2672,25 @@
         <v>2.66</v>
       </c>
       <c r="AA14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.17</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.03</v>
+        <v>7.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S16" t="n">
         <v>1.44</v>
@@ -2972,44 +2972,44 @@
         <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O18" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>1.5</v>
@@ -3299,13 +3299,13 @@
         <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
         <v>1.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="AA18" t="n">
         <v>2.5</v>
@@ -3320,13 +3320,13 @@
         <v>1.12</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>5.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>9.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>5.45</v>
       </c>
       <c r="P8" t="n">
-        <v>5.03</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>6.1</v>
       </c>
       <c r="U8" t="n">
-        <v>3.18</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.04</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.19</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>5.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.96</v>
+        <v>1.37</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>2.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.02</v>
+        <v>1.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,49 +1838,49 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
         <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1889,13 +1889,13 @@
         <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>5.45</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>5.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>6.1</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.57</v>
       </c>
-      <c r="V10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.17</v>
       </c>
-      <c r="AB10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.7</v>
+        <v>5.35</v>
       </c>
       <c r="R11" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.07</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>7.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="S14" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
         <v>4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.35</v>
+        <v>7.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.55</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>7.21</v>
+        <v>3.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
         <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>4.59</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.4</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>3.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>7.39</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>3.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>5.45</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.3</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V8" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.17</v>
       </c>
-      <c r="AB8" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>5.45</v>
       </c>
       <c r="P10" t="n">
-        <v>5.03</v>
+        <v>1.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>3.18</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.96</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>2.69</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.35</v>
+        <v>7.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.55</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>7.21</v>
+        <v>3.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="R14" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.75</v>
+        <v>1.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>5.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.02</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.04</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.48</v>
+        <v>7.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
         <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>2.39</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="O17" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="P17" t="n">
         <v>11</v>
@@ -3122,22 +3122,22 @@
         <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>3.61</v>
+        <v>3.13</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -3149,19 +3149,19 @@
         <v>8.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
         <v>1.53</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.35</v>
+        <v>4.47</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
         <v>2</v>
@@ -3287,7 +3287,7 @@
         <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U18" t="n">
         <v>3.5</v>
@@ -3296,22 +3296,22 @@
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
         <v>4.65</v>
@@ -3320,13 +3320,13 @@
         <v>1.12</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.28</v>
+        <v>2.53</v>
       </c>
       <c r="O19" t="n">
-        <v>5.05</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>9.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,52 +1679,52 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
         <v>1.17</v>
@@ -1736,7 +1736,7 @@
         <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
         <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>5.45</v>
+        <v>3.62</v>
       </c>
       <c r="P10" t="n">
-        <v>1.22</v>
+        <v>6.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>3.08</v>
       </c>
       <c r="V10" t="n">
-        <v>2.31</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.36</v>
+        <v>3.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.69</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.06</v>
+        <v>2.39</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.75</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>3.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.7</v>
+        <v>2.77</v>
       </c>
       <c r="R11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.35</v>
+        <v>2.29</v>
       </c>
       <c r="R12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.98</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>3.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U14" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="V14" t="n">
         <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.03</v>
+        <v>1.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>8.15</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>7.21</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="U16" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.88</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AG16" t="n">
         <v>1.57</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.39</v>
+        <v>1.11</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3119,34 +3119,34 @@
         <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
         <v>1.25</v>
@@ -3155,13 +3155,13 @@
         <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AD17" t="n">
         <v>1.91</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
         <v>1.53</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
         <v>4.47</v>
@@ -3275,37 +3275,37 @@
         <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T18" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA18" t="n">
         <v>2.4</v>
@@ -3314,13 +3314,13 @@
         <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
         <v>2.14</v>
@@ -3342,7 +3342,7 @@
         <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="O20" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
         <v>7.3</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>8.15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
@@ -1859,10 +1859,10 @@
         <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
@@ -1871,31 +1871,31 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.62</v>
+        <v>5.45</v>
       </c>
       <c r="P10" t="n">
-        <v>6.25</v>
+        <v>1.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.16</v>
+        <v>3.36</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>6.1</v>
       </c>
       <c r="U10" t="n">
-        <v>3.08</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.39</v>
+        <v>1.06</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>3.58</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.77</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>5.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.29</v>
+        <v>5.75</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="U12" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.92</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
         <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.09</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>1.76</v>
       </c>
       <c r="O13" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.22</v>
+        <v>4.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>2.47</v>
       </c>
       <c r="R13" t="n">
-        <v>3.36</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>6.1</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>3.15</v>
       </c>
       <c r="V13" t="n">
-        <v>2.32</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>2.19</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.14</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,55 +2633,55 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="V14" t="n">
         <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
@@ -2690,7 +2690,7 @@
         <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.15</v>
+        <v>2.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>4.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="S16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.64</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.53</v>
+        <v>1.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.23</v>
+        <v>2.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>5.45</v>
       </c>
       <c r="P8" t="n">
-        <v>3.35</v>
+        <v>1.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>3.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>6.1</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>2.32</v>
       </c>
       <c r="W8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.03</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.63</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.15</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
@@ -1871,31 +1871,31 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.45</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.03</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.31</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>4.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.64</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>5.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>5.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="S14" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.96</v>
+        <v>3.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.88</v>
+        <v>1.09</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>4.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB15" t="n">
         <v>1.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="O16" t="n">
         <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>4.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="AD16" t="n">
         <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.23</v>
+        <v>2.53</v>
       </c>
       <c r="O19" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>1.23</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA2" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '60']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '18', '26']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46205.375</v>
@@ -852,25 +852,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="P3" t="n">
-        <v>3.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46205.375</v>
@@ -1011,19 +1011,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1035,72 +1035,72 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="O4" t="n">
         <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1109,14 +1109,14 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71', '90+2']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1179,36 +1179,36 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>4.91</v>
       </c>
       <c r="P5" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>['30', '35', '42', '80', '90']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46205.45833333334</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.39</v>
+        <v>7.49</v>
       </c>
       <c r="R7" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>1.76</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>4.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.15</v>
+        <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
         <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.4</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
         <v>1.57</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.87</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.07</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
         <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.31</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>4.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="S14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.64</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>8.15</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -2981,50 +2981,50 @@
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.75</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O18" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S18" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T18" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3596,34 +3596,34 @@
         <v>7.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
@@ -3632,19 +3632,19 @@
         <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -693,31 +693,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -725,107 +725,107 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
         <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>['20', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>['15', '18', '26']</t>
+          <t>['71', '90+2']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46205.375</v>
@@ -1011,31 +1011,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
         <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>3.17</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '60']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['71', '90+2']</t>
+          <t>['15', '18', '26']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46205.375</v>
@@ -1338,130 +1338,130 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
         <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '13', '15', '27', '45', '59']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86', '90+1']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1500,23 +1500,23 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '54', '60']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1637,149 +1637,149 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>5.45</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.22</v>
+        <v>3.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>2.49</v>
       </c>
       <c r="R8" t="n">
-        <v>3.36</v>
+        <v>1.99</v>
       </c>
       <c r="S8" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>6.1</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>3.08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.32</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>1.42</v>
       </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46205.58333333334</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1993,111 +1993,111 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.31</v>
+        <v>5.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>5.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>3.92</v>
+        <v>2.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '59', '87']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+6']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2304,118 +2304,118 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
         <v>1.96</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
         <v>2.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>['54', '77']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1</v>
-      </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2432,149 +2432,149 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.44</v>
+        <v>6.57</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>7.3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.75</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.59</v>
+        <v>5.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.94</v>
+        <v>1.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>2.97</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>1.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>3.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '10', '13']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '71', '84']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2601,16 +2601,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2622,118 +2622,118 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.07</v>
+        <v>4.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>['83', '90+4']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="R15" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S15" t="n">
         <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U15" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.15</v>
+        <v>5.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>5.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.79</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,40 +3110,40 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z17" t="n">
         <v>9</v>
@@ -3155,19 +3155,19 @@
         <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
         <v>1.91</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.47</v>
+        <v>5.05</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.53</v>
+        <v>1.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="S19" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T19" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.37</v>
+        <v>3.23</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P20" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="R20" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.32</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>3.23</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,28 +1329,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>6.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['3', '13', '15', '27', '45', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['86', '90+1']</t>
+          <t>['29', '54', '60']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.07</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
         <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AS6" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="AT6" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,28 +1488,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.75</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.49</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '13', '15', '27', '45', '59']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['29', '54', '60']</t>
+          <t>['86', '90+1']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>2.07</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1647,28 +1647,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.49</v>
+        <v>5.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="S8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.4</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1761,25 +1761,25 @@
         <v>3</v>
       </c>
       <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
         <v>5</v>
       </c>
-      <c r="AO8" t="n">
-        <v>12</v>
-      </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.2</v>
+        <v>0.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="AT8" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46205.58333333334</v>
@@ -1796,149 +1796,149 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="P9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['2', '10', '13']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['36', '71', '84']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
         <v>4</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46205.58333333334</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1980,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="R10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.95</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2079,25 +2079,25 @@
         <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
         <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AT10" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2283,28 +2283,28 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U12" t="n">
         <v>3.25</v>
       </c>
-      <c r="P12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.66</v>
       </c>
-      <c r="AC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['54', '77']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.71</v>
+        <v>1.62</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.29</v>
+        <v>0.87</v>
       </c>
       <c r="AS12" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="AT12" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2432,149 +2432,149 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>['19', '45+1']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>['16', '28']</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>['2', '10', '13']</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>['36', '71', '84']</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>10</v>
       </c>
-      <c r="AO13" t="n">
-        <v>8</v>
-      </c>
       <c r="AP13" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.99</v>
+        <v>1.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.94</v>
+        <v>0.45</v>
       </c>
       <c r="AS13" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AT13" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2760,16 +2760,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2781,39 +2781,39 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>6.67</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
@@ -2822,77 +2822,77 @@
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
         <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>['54', '77']</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2919,16 +2919,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2940,118 +2940,118 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>1.52</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>6.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.74</v>
+        <v>2.09</v>
       </c>
       <c r="R16" t="n">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="U16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>['80', '90+9']</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
         <v>4</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AN16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.2</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46205.58333333334</v>
@@ -3087,130 +3087,130 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="O17" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>11.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="S17" t="n">
         <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="W17" t="n">
         <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '82', '90+5']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '23']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.05</v>
+        <v>5.45</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46205.67708333334</v>
@@ -3269,37 +3269,37 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
         <v>1.44</v>
@@ -3308,22 +3308,22 @@
         <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
         <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
         <v>1.6</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
         <v>1.91</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P19" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="R19" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.32</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>3.23</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK20" t="n">
         <v>3.34</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-02.xlsx
+++ b/jogos_2026-07-02.xlsx
@@ -852,29 +852,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -884,104 +884,104 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['20', '60']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['15', '18', '26']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7</v>
+        <v>1.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="AT3" t="n">
         <v>67</v>
@@ -1011,136 +1011,136 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['20', '60']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['15', '18', '26']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2</v>
       </c>
-      <c r="AN4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.86</v>
+        <v>0.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AT4" t="n">
         <v>67</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,28 +1329,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.75</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.49</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '13', '15', '27', '45', '59']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['29', '54', '60']</t>
+          <t>['86', '90+1']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>2.07</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
         <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AS6" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,28 +1488,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>6.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['3', '13', '15', '27', '45', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['86', '90+1']</t>
+          <t>['29', '54', '60']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.07</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="AT7" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46205.54166666666</v>
@@ -1796,32 +1796,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.57</v>
+        <v>2.33</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>7.3</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>['2', '10', '13']</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>['36', '71', '84']</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP9" t="n">
         <v>8</v>
       </c>
-      <c r="AP9" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>0.99</v>
+        <v>1.62</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.94</v>
+        <v>0.87</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="AT9" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46205.58333333334</v>
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.99</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2027,77 +2027,77 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
         <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['83', '90+4']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.42</v>
+        <v>2.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="AT10" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>['54', '77']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>15</v>
-      </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.62</v>
+        <v>0.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AT12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2442,28 +2442,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2474,34 +2474,34 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
@@ -2510,71 +2510,71 @@
         <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
         <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.76</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>['19', '45+1']</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>['16', '28']</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.45</v>
+        <v>1.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="AT13" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2591,149 +2591,149 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.6</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>6.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>7.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="W14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.03</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>['2', '10', '13']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>['36', '71', '84']</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>['83', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO14" t="n">
         <v>8</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>24</v>
-      </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.75</v>
+        <v>0.99</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="AS14" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="AT14" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46205.58333333334</v>
@@ -2760,28 +2760,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2792,107 +2792,107 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S15" t="n">
         <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
         <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>['54', '77']</t>
+          <t>['19', '45+1']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '28']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AS15" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="AT15" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46205.58333333334</v>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3258,14 +3258,14 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3348,28 +3348,28 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46205.83333333334</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
         <v>4.4</v>
@@ -3596,49 +3596,49 @@
         <v>7.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U20" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF20" t="n">
         <v>2.15</v>
@@ -3660,7 +3660,7 @@
         <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
